--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ml_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ml_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>24-11-2021 08:30</t>
+          <t>2021-11-24 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14218,7 +14218,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15356,7 +15356,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16302,7 +16302,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>04-11-2021 08:30</t>
+          <t>2021-04-11 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16682,7 +16682,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>04-11-2021 08:30</t>
+          <t>2021-04-11 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17442,7 +17442,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>04-11-2021 08:30</t>
+          <t>2021-04-11 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18107,7 +18107,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18867,7 +18867,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>04-11-2021 08:30</t>
+          <t>2021-04-11 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19243,7 +19243,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19336,7 +19336,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19429,7 +19429,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -19987,7 +19987,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20173,7 +20173,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20452,7 +20452,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -20824,7 +20824,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -20917,7 +20917,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -21010,7 +21010,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21103,7 +21103,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21196,7 +21196,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21475,7 +21475,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21661,7 +21661,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -21754,7 +21754,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -21847,7 +21847,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -21940,7 +21940,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -22033,7 +22033,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22312,7 +22312,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22498,7 +22498,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22684,7 +22684,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -22870,7 +22870,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -22963,7 +22963,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23056,7 +23056,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23149,7 +23149,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23242,7 +23242,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23335,7 +23335,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23428,7 +23428,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23614,7 +23614,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23707,7 +23707,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -23800,7 +23800,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -23893,7 +23893,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24079,7 +24079,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24172,7 +24172,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24265,7 +24265,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24358,7 +24358,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24451,7 +24451,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="inlineStr"/>
@@ -24544,7 +24544,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="inlineStr"/>
@@ -24637,7 +24637,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr"/>
@@ -24730,7 +24730,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="inlineStr"/>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="inlineStr"/>
@@ -24916,7 +24916,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="inlineStr"/>
@@ -25009,7 +25009,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="inlineStr"/>
@@ -25102,7 +25102,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr"/>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25474,7 +25474,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="inlineStr"/>
@@ -25567,7 +25567,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="inlineStr"/>
@@ -25660,7 +25660,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="inlineStr"/>
@@ -25753,7 +25753,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="inlineStr"/>
@@ -25846,7 +25846,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26032,7 +26032,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="n">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="n">
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26317,7 +26317,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -26507,7 +26507,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -26602,7 +26602,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="n">
@@ -26697,7 +26697,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
